--- a/data.xlsx
+++ b/data.xlsx
@@ -3199,7 +3199,7 @@
         <v>285</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>423</v>
+        <v>172</v>
       </c>
       <c r="D78" s="27" t="s">
         <v>287</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="437">
   <si>
     <t/>
   </si>
@@ -1320,13 +1320,22 @@
   </si>
   <si>
     <t>中速慢速</t>
+  </si>
+  <si>
+    <t>快攻 中速</t>
+  </si>
+  <si>
+    <t>快攻 otk</t>
+  </si>
+  <si>
+    <t>中速 快攻</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Microsoft YaHei"/>
     </font>
@@ -1417,8 +1426,11 @@
     <font>
       <name val="Microsoft YaHei"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1456,6 +1468,7 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill/>
   </fills>
   <borders count="2">
     <border>
@@ -1474,11 +1487,11 @@
     </border>
   </borders>
   <cellStyleXfs>
-    <xf fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1572,6 +1585,12 @@
     <xf fontId="19" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="20" fillId="8" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="7" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1588,49 +1607,7 @@
   <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE5F6FF"/>
-          <bgColor rgb="FFE5F6FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00A3F5"/>
-          <bgColor rgb="FF00A3F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="TENCENT_DOCS_BUILD_IN_TABLE_STYLE_ROW_normal_#00A3F5" table="1" count="4">
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
-      <tableStyleElement type="firstColumn" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="1"/>
-    </tableStyle>
-  </tableStyles>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表_1806402390" displayName="表_1806402390" ref="B300:B301" headerRowCount="1" totalsRowCount="0">
-  <autoFilter ref="B300:B301">
-    <sortState ref="B301"/>
-  </autoFilter>
-  <tableColumns count="1">
-    <tableColumn id="1" name="列1"/>
-  </tableColumns>
-  <tableStyleInfo name="TENCENT_DOCS_BUILD_IN_TABLE_STYLE_ROW_normal_#00A3F5" showFirstColumn="0" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1868,18 +1845,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor/>
   </sheetPr>
-  <dimension ref="E301"/>
+  <dimension ref="E300"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.2109" style="31" customWidth="1"/>
-    <col min="2" max="2" width="36.4219" style="32" customWidth="1"/>
-    <col min="3" max="3" width="38.0312" style="33" customWidth="1"/>
-    <col min="4" max="4" width="53.0469" style="34" customWidth="1"/>
-    <col min="5" max="5" width="34.2617" style="34" customWidth="1"/>
+    <col min="1" max="1" width="18.2109" style="33" customWidth="1"/>
+    <col min="2" max="2" width="36.4219" style="34" customWidth="1"/>
+    <col min="3" max="3" width="38.0312" style="35" customWidth="1"/>
+    <col min="4" max="4" width="53.0469" style="36" customWidth="1"/>
+    <col min="5" max="5" width="34.2617" style="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1">
@@ -1991,8 +1968,8 @@
       <c r="B7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
+      <c r="C7" s="32" t="s">
+        <v>434</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>32</v>
@@ -2110,8 +2087,8 @@
       <c r="B14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>59</v>
+      <c r="C14" s="20" t="s">
+        <v>435</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>60</v>
@@ -2484,8 +2461,8 @@
       <c r="B36" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>142</v>
+      <c r="C36" s="20" t="s">
+        <v>436</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>143</v>
@@ -2535,8 +2512,8 @@
       <c r="B39" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>153</v>
+      <c r="C39" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>154</v>
@@ -2841,8 +2818,8 @@
       <c r="B57" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>153</v>
+      <c r="C57" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>216</v>
@@ -2926,8 +2903,8 @@
       <c r="B62" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>153</v>
+      <c r="C62" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>234</v>
@@ -3368,8 +3345,8 @@
       <c r="B88" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>153</v>
+      <c r="C88" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="D88" s="11" t="s">
         <v>320</v>
@@ -3419,8 +3396,8 @@
       <c r="B91" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>153</v>
+      <c r="C91" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="D91" s="26" t="s">
         <v>329</v>
@@ -5125,28 +5102,13 @@
       <c r="D299" s="5" t="s"/>
       <c r="E299" s="5" t="s"/>
     </row>
-    <row r="300" spans="2:2">
-      <c r="B300" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" ht="60" customHeight="1">
-      <c r="A301" s="11" t="s"/>
-      <c r="B301" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="C301" s="10" t="s"/>
-      <c r="D301" s="29" t="s"/>
-      <c r="E301" s="29" t="s">
-        <v>421</v>
-      </c>
+    <row r="300" spans="1:5" ht="60" customHeight="1">
+      <c r="A300" s="11" t="s"/>
+      <c r="B300" s="30" t="s"/>
+      <c r="C300" s="10" t="s"/>
+      <c r="D300" s="29" t="s"/>
+      <c r="E300" s="29" t="s"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A117">
-    <sortState ref="A2:A117"/>
-  </autoFilter>
-  <tableParts count="1">
-    <tablePart r:id="rId0"/>
-  </tableParts>
 </worksheet>
 </file>